--- a/qc/spreadsheets/ugr_qc.xlsx
+++ b/qc/spreadsheets/ugr_qc.xlsx
@@ -464,8 +464,8 @@
     <col width="20" customWidth="1" min="17" max="17"/>
     <col width="45" customWidth="1" min="18" max="18"/>
     <col width="13" customWidth="1" min="19" max="19"/>
-    <col width="45" customWidth="1" min="20" max="20"/>
-    <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="17" customWidth="1" min="20" max="20"/>
+    <col width="11" customWidth="1" min="21" max="21"/>
     <col width="45" customWidth="1" min="22" max="22"/>
     <col width="45" customWidth="1" min="23" max="23"/>
     <col width="45" customWidth="1" min="24" max="24"/>
@@ -29425,6 +29425,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="F317" t="n">
+        <v>51.89359670563135</v>
+      </c>
+      <c r="G317" t="n">
+        <v>0.1766036671950174</v>
+      </c>
       <c r="H317" t="n">
         <v>22</v>
       </c>
@@ -29440,6 +29446,12 @@
       <c r="L317" t="n">
         <v>99.54567192730751</v>
       </c>
+      <c r="M317" t="b">
+        <v>0</v>
+      </c>
+      <c r="N317" t="b">
+        <v>0</v>
+      </c>
       <c r="O317" t="b">
         <v>0</v>
       </c>
@@ -29450,21 +29462,21 @@
         <v>0</v>
       </c>
       <c r="S317" t="b">
-        <v>0</v>
-      </c>
-      <c r="T317" t="inlineStr">
-        <is>
-          <t>fd_mean:missing_mriqc_json;tsnr:missing_mriqc_json</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="U317" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>pass</t>
         </is>
       </c>
       <c r="V317" t="inlineStr">
         <is>
           <t>bids/sub-11078/ses-02/func/sub-11078_ses-02_task-ugr_run-1_echo-2_part-mag_bold.nii.gz</t>
+        </is>
+      </c>
+      <c r="W317" t="inlineStr">
+        <is>
+          <t>derivatives/mriqc/sub-11078/ses-02/func/sub-11078_ses-02_task-ugr_run-1_echo-2_part-mag_bold.json</t>
         </is>
       </c>
       <c r="X317" t="inlineStr">
@@ -29504,6 +29516,12 @@
           <t>2</t>
         </is>
       </c>
+      <c r="F318" t="n">
+        <v>38.10938572254963</v>
+      </c>
+      <c r="G318" t="n">
+        <v>0.192009843250243</v>
+      </c>
       <c r="H318" t="n">
         <v>57</v>
       </c>
@@ -29519,6 +29537,12 @@
       <c r="L318" t="n">
         <v>99.61209416015728</v>
       </c>
+      <c r="M318" t="b">
+        <v>0</v>
+      </c>
+      <c r="N318" t="b">
+        <v>0</v>
+      </c>
       <c r="O318" t="b">
         <v>0</v>
       </c>
@@ -29529,21 +29553,21 @@
         <v>0</v>
       </c>
       <c r="S318" t="b">
-        <v>0</v>
-      </c>
-      <c r="T318" t="inlineStr">
-        <is>
-          <t>fd_mean:missing_mriqc_json;tsnr:missing_mriqc_json</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="U318" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>pass</t>
         </is>
       </c>
       <c r="V318" t="inlineStr">
         <is>
           <t>bids/sub-11078/ses-02/func/sub-11078_ses-02_task-ugr_run-2_echo-2_part-mag_bold.nii.gz</t>
+        </is>
+      </c>
+      <c r="W318" t="inlineStr">
+        <is>
+          <t>derivatives/mriqc/sub-11078/ses-02/func/sub-11078_ses-02_task-ugr_run-2_echo-2_part-mag_bold.json</t>
         </is>
       </c>
       <c r="X318" t="inlineStr">
@@ -65697,7 +65721,7 @@
     <col width="28" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
@@ -65779,22 +65803,22 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="E2" t="n">
-        <v>25.84464742220007</v>
+        <v>25.86456660646945</v>
       </c>
       <c r="F2" t="n">
-        <v>39.93214645679109</v>
+        <v>39.93891579844058</v>
       </c>
       <c r="G2" t="n">
-        <v>14.08749903459102</v>
+        <v>14.07434919197112</v>
       </c>
       <c r="H2" t="n">
-        <v>4.71339887031354</v>
+        <v>4.753042818512768</v>
       </c>
       <c r="I2" t="n">
-        <v>61.06339500867762</v>
+        <v>61.05043958639726</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -65822,22 +65846,22 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1221545945729896</v>
+        <v>0.1222637127509929</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2443201046930438</v>
+        <v>0.244217014456858</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1221655101200542</v>
+        <v>0.1219533017058651</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.06109367060709173</v>
+        <v>-0.06066623980780482</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4275683698731251</v>
+        <v>0.4271469670156557</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
